--- a/artfynd/A 59300-2025 artfynd.xlsx
+++ b/artfynd/A 59300-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99128277</v>
+        <v>99128252</v>
       </c>
       <c r="B2" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>364601.2570785574</v>
+        <v>364602</v>
       </c>
       <c r="R2" t="n">
-        <v>6618806.067111033</v>
+        <v>6618802</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,22 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -813,6 +798,266 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Högvalta, invetering av brun gräsfjäril inom planprogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>99128275</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>slaghåvning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>högvalta, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>364613</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6618797</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fynd inom Inventering av brun gräsfjäril Coenonympha hero inom planprogram Högvalta, Arvika kommun</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Henric Ernstson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henric Ernstson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Högvalta, invetering av brun gräsfjäril inom planprogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99128277</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>slaghåvning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>högvalta, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>364602</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6618806</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fynd inom Inventering av brun gräsfjäril Coenonympha hero inom planprogram Högvalta, Arvika kommun</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henric Ernstson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henric Ernstson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Högvalta, invetering av brun gräsfjäril inom planprogram</t>
         </is>
